--- a/Histórico de culturas.xlsx
+++ b/Histórico de culturas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1cc81c05594695/Dashboards/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{B663FA9D-63D9-4817-B51A-83BC726D2529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBB801BE-9220-B342-90A1-2BA7DF5989DD}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{B663FA9D-63D9-4817-B51A-83BC726D2529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BF15B43-42DF-A94F-B5C4-2D787DE5B4A4}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15220" xr2:uid="{EC402824-E070-4638-AB0F-B9DF5E3FF754}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="416">
   <si>
     <t>quinta</t>
   </si>
@@ -1262,30 +1262,6 @@
     <t>Kumato / 6</t>
   </si>
   <si>
-    <t>Par / Estufa 33-2026</t>
-  </si>
-  <si>
-    <t>San / Estufa 33-2026</t>
-  </si>
-  <si>
-    <t>mini kumato / Estufa 33-2026</t>
-  </si>
-  <si>
-    <t>Cyg / Estufa 33-2026</t>
-  </si>
-  <si>
-    <t>PARISETTO/ Inv 2 Crist-2026</t>
-  </si>
-  <si>
-    <t>CYGNARY / Inv 2 Crist-2026</t>
-  </si>
-  <si>
-    <t>BRONSKI / Inv 1 Plast-2026</t>
-  </si>
-  <si>
-    <t>SANBLAAS / Inv 1 Plast-2026</t>
-  </si>
-  <si>
     <t>TIAC / V10</t>
   </si>
   <si>
@@ -1293,6 +1269,27 @@
   </si>
   <si>
     <t>BRONSKY / V9</t>
+  </si>
+  <si>
+    <t>Parisetto</t>
+  </si>
+  <si>
+    <t>San Blas</t>
+  </si>
+  <si>
+    <t>Keisha</t>
+  </si>
+  <si>
+    <t>PARISETTO 2</t>
+  </si>
+  <si>
+    <t>CYGNARY 2</t>
+  </si>
+  <si>
+    <t>BRONSKI 1</t>
+  </si>
+  <si>
+    <t>SANBLAAS 1</t>
   </si>
 </sst>
 </file>
@@ -1726,7 +1723,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5" style="6" customWidth="1"/>
     <col min="4" max="4" width="11.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" style="10" customWidth="1"/>
@@ -19005,7 +19002,7 @@
         <v>18</v>
       </c>
       <c r="B463" s="6" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C463" s="9">
         <v>2026</v>
@@ -19040,7 +19037,7 @@
         <v>18</v>
       </c>
       <c r="B464" s="6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C464" s="9">
         <v>2026</v>
@@ -19075,7 +19072,7 @@
         <v>18</v>
       </c>
       <c r="B465" s="6" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C465" s="9">
         <v>2026</v>
@@ -19110,7 +19107,7 @@
         <v>18</v>
       </c>
       <c r="B466" s="6" t="s">
-        <v>409</v>
+        <v>244</v>
       </c>
       <c r="C466" s="9">
         <v>2026</v>
@@ -19145,7 +19142,7 @@
         <v>15</v>
       </c>
       <c r="B467" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C467" s="9">
         <v>2026</v>
@@ -19180,7 +19177,7 @@
         <v>15</v>
       </c>
       <c r="B468" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C468" s="9">
         <v>2026</v>
@@ -19215,7 +19212,7 @@
         <v>15</v>
       </c>
       <c r="B469" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C469" s="9">
         <v>2026</v>
@@ -19250,7 +19247,7 @@
         <v>15</v>
       </c>
       <c r="B470" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C470" s="9">
         <v>2026</v>
@@ -19355,7 +19352,7 @@
         <v>14</v>
       </c>
       <c r="B473" s="6" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C473" s="9">
         <v>2026</v>
@@ -19390,7 +19387,7 @@
         <v>14</v>
       </c>
       <c r="B474" s="6" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="C474" s="9">
         <v>2026</v>
@@ -19425,7 +19422,7 @@
         <v>14</v>
       </c>
       <c r="B475" s="6" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C475" s="9">
         <v>2026</v>
